--- a/ProjectDescription/ytdlp_bridge_FunctionNameReg.xlsx
+++ b/ProjectDescription/ytdlp_bridge_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1176,390 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>downloadVideoWithProgress</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>video_url&lt;String&gt;, format_id&lt;String&gt;, output_dir&lt;String&gt;, cookie_file&lt;String&gt;, progress_file&lt;String&gt;, cancel_flag_file&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>下载视频并支持进度回调和取消操作</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[downloadVideoWithProgress:189]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>支持进度文件写入和取消标志检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ytdlp_bridge</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Python桥接模块，通过Chaquopy在Android中运行，提供yt-dlp的封装接口</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[ytdlp_bridge:1]</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>包含环境检测和视频信息提取功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>testEnvironment</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>测试Python运行环境，返回Python版本和yt-dlp安装状态</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[testEnvironment:12]</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>返回JSON格式字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>extractVideoInfo</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>video_url&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>提取指定视频链接的信息，使用yt-dlp获取标题、格式、时长等元数据</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[extractVideoInfo:55]</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>返回JSON格式字符串，包含可用格式列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ytdlp_bridge</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Python桥接模块，通过Chaquopy在Android中运行，提供yt-dlp的封装接口</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[ytdlp_bridge:1]</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>包含环境检测和视频信息提取功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>testEnvironment</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>测试Python运行环境，返回Python版本和yt-dlp安装状态</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[testEnvironment:12]</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>返回JSON格式字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>extractVideoInfo</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>video_url&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>提取指定视频链接的信息，使用yt-dlp获取标题、格式、时长等元数据</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[extractVideoInfo:55]</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>返回JSON格式字符串，包含可用格式列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ytdlp_bridge</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Python桥接模块，通过Chaquopy在Android中运行，提供yt-dlp的封装接口</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[ytdlp_bridge:1]</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>包含环境检测和视频信息提取功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>testEnvironment</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>测试Python运行环境，返回Python版本和yt-dlp安装状态</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[testEnvironment:12]</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>返回JSON格式字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>extractVideoInfo</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>函数</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>video_url&lt;str&gt;</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>提取指定视频链接的信息，使用yt-dlp获取标题、格式、时长等元数据</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[extractVideoInfo:55]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>返回JSON格式字符串，包含可用格式列表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/ytdlp_bridge_FunctionNameReg.xlsx
+++ b/ProjectDescription/ytdlp_bridge_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -774,6 +774,116 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>_FFMPEG_PATH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>全局FFmpeg路径缓存，供下载函数中使用，由check_ffmpeg_available设置</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[_FFMPEG_PATH:28]</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月20日13时12分54秒</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>全局作用域，多个函数共享</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>use_media_muxer</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>MediaMuxer合并标志，当FFmpeg不可用且无已合并格式时设为True，触发Java层合并</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[use_media_muxer:566]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月20日13时12分54秒</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>在formatId策略中设置，在下载阶段使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>downloadVideoWithProgress（MediaMuxer合并逻辑）</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>逻辑段</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>当use_media_muxer为True时：1.下载音频流 2.调用Java MediaMuxerHelper合并 3.清理临时文件</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/python/ytdlp_bridge.py)[downloadVideoWithProgress-&gt;MediaMuxer合并:719-809]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月20日13时12分54秒</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>通过jclass桥接调用Java静态方法mergeVideoAudio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
